--- a/data/test/selections.xlsx
+++ b/data/test/selections.xlsx
@@ -397,10 +397,831 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:F41"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>weekLabel</v>
+      </c>
+      <c r="C1" t="str">
+        <v>customerId</v>
+      </c>
+      <c r="D1" t="str">
+        <v>day</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mealNum</v>
+      </c>
+      <c r="F1" t="str">
+        <v>menuSlot</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-W20-0901000002-1-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-W20</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0901000002</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-W20-0901000005-1-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-W20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-W19-0901000001-1-1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>0901000001</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-W19-0901000002-1-1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>0901000002</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-W19-0901000004-1-1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-W19-0901000003-1-1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>0901000003</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-W19-0901000004-1-2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-W19-0901000005-1-1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-W19-0901000006-1-1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C10" t="str">
+        <v>0901000006</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-W19-0901000007-1-1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C11" t="str">
+        <v>0901000007</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-W19-0901000007-1-2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C12" t="str">
+        <v>0901000007</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-W19-0901000008-1-1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C13" t="str">
+        <v>0901000008</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-W19-0901000009-1-1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C14" t="str">
+        <v>0901000009</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-W19-0901000010-1-1</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C15" t="str">
+        <v>0901000010</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-W19-0901000010-1-2</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C16" t="str">
+        <v>0901000010</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-W19-0901000011-1-1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C17" t="str">
+        <v>0901000011</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-W19-0901000012-1-1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C18" t="str">
+        <v>0901000012</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-W19-0901000013-1-1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C19" t="str">
+        <v>0901000013</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-W19-0901000013-1-2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C20" t="str">
+        <v>0901000013</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-W19-0901000001-2-1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C21" t="str">
+        <v>0901000001</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-W19-0901000001-3-2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C22" t="str">
+        <v>0901000001</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-W19-0901000004-3-2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C23" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-W19-0901000003-2-1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C24" t="str">
+        <v>0901000003</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-W19-0901000004-2-1</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C25" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-W19-0901000005-2-1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C26" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-W19-0901000006-2-1</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C27" t="str">
+        <v>0901000006</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-W19-0901000004-4-1</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C28" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-W19-0901000004-4-2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C29" t="str">
+        <v>0901000004</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-W19-0901000005-4-1</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C30" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-W19-0901000006-4-1</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C31" t="str">
+        <v>0901000006</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-W19-0901000007-4-1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C32" t="str">
+        <v>0901000007</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-W19-0901000008-4-1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C33" t="str">
+        <v>0901000008</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-W19-0901000010-4-1</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C34" t="str">
+        <v>0901000010</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-W19-0901000009-4-1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C35" t="str">
+        <v>0901000009</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-W19-0901000011-4-1</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C36" t="str">
+        <v>0901000011</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-W19-0901000012-4-1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C37" t="str">
+        <v>0901000012</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-W19-0901000013-4-1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C38" t="str">
+        <v>0901000013</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-W19-0901000014-4-1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C39" t="str">
+        <v>0901000014</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-W19-0901000015-4-1</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C40" t="str">
+        <v>0901000015</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-W19-0901000016-4-1</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-W19</v>
+      </c>
+      <c r="C41" t="str">
+        <v>0901000016</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/test/selections.xlsx
+++ b/data/test/selections.xlsx
@@ -397,111 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>weekLabel</v>
-      </c>
-      <c r="C1" t="str">
-        <v>customerId</v>
-      </c>
-      <c r="D1" t="str">
-        <v>day</v>
-      </c>
-      <c r="E1" t="str">
-        <v>mealNum</v>
-      </c>
-      <c r="F1" t="str">
-        <v>menuSlot</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-W20-0901000026-1-1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0901000026</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-W20-0901000013-1-1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0901000013</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2026-W20-0368980079-1-1</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C4" t="str">
-        <v>0368980079</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-W20-0368980079-1-2</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C5" t="str">
-        <v>0368980079</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>